--- a/output/pdf_financials_xlsx/PWER.xlsx
+++ b/output/pdf_financials_xlsx/PWER.xlsx
@@ -5949,52 +5949,52 @@
         <v>0.797014</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.847233</v>
+        <v>0.917233</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.857773</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.934883</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.93124</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.264601</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.264601</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.877903</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.877903</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.877903</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.872915</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.872915</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.932155</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.923417</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.910011</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.903786</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.903786</v>
       </c>
     </row>
     <row r="93">
@@ -9822,7 +9822,11 @@
           <t>Share based payment reserves 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -12091,7 +12095,11 @@
           <t>Share based payment reserves 8</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -15223,7 +15231,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -16419,7 +16431,11 @@
           <t>Share based payment reserve 8</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -18017,7 +18033,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -19702,7 +19722,11 @@
           <t>Share-based payment reserves 8</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -21417,7 +21441,11 @@
           <t>Share based payment reserve 12</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -23411,7 +23439,11 @@
           <t>Share based payment reserve 12</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -25322,7 +25354,11 @@
           <t>Share based payment reserve 11</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -26940,7 +26976,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28140,7 +28180,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -28635,7 +28679,11 @@
           <t>$                                                                                              Reserves  $</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PWER.xlsx
+++ b/output/pdf_financials_xlsx/PWER.xlsx
@@ -2368,55 +2368,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.360949</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.306375</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.252622</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.049262</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.06406100000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.056117</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.006007</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.171059</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07951</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.067451</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010659</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.007943</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.08809500000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.063966</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.013907</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.017165</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.034507</v>
       </c>
     </row>
     <row r="35">
@@ -2484,55 +2484,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.472043</v>
+        <v>0.832992</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.318863</v>
+        <v>0.625238</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.31419</v>
+        <v>0.566812</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.008059999999999999</v>
+        <v>0.057322</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.048198</v>
+        <v>0.112259</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.220864</v>
+        <v>0.276981</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.22074</v>
+        <v>0.226747</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.021499</v>
+        <v>0.192558</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.022245</v>
+        <v>0.101755</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.031763</v>
+        <v>0.099214</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.030993</v>
+        <v>0.041652</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.02057</v>
+        <v>0.028513</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.018789</v>
+        <v>0.106884</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.018002</v>
+        <v>0.081968</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.018237</v>
+        <v>0.032144</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.018028</v>
+        <v>0.035193</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.035899</v>
+        <v>0.070406</v>
       </c>
     </row>
     <row r="37">
@@ -3180,55 +3180,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.891387</v>
+        <v>0.530438</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.657701</v>
+        <v>0.351326</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.59894</v>
+        <v>0.346318</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.246599</v>
+        <v>0.197337</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.23705</v>
+        <v>0.172989</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.092097</v>
+        <v>0.03598</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.025032</v>
+        <v>0.019025</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.323421</v>
+        <v>0.152362</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.141321</v>
+        <v>0.061811</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.121049</v>
+        <v>0.053598</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.037054</v>
+        <v>0.026395</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.034387</v>
+        <v>0.026444</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.111629</v>
+        <v>0.023534</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.086697</v>
+        <v>0.022731</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.03689</v>
+        <v>0.022983</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.039751</v>
+        <v>0.022586</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.038708</v>
+        <v>0.004201</v>
       </c>
     </row>
     <row r="49">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/PWER.xlsx
+++ b/output/pdf_financials_xlsx/PWER.xlsx
@@ -7092,13 +7092,13 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.007882</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.021106</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.012413</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -44715,7 +44715,11 @@
           <t>Proceeds on disposal of property, plant &amp; equipment</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -46414,7 +46418,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PWER.xlsx
+++ b/output/pdf_financials_xlsx/PWER.xlsx
@@ -1574,11 +1574,15 @@
       <c r="C20" s="3" t="n">
         <v>-1.212957</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>-1.105029</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-1.054624</v>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.492176</v>
@@ -1598,11 +1602,15 @@
       <c r="K20" s="3" t="n">
         <v>0.14504</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>-0.144562</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0.013135</v>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N20" s="3" t="n">
         <v>-0.282382</v>
@@ -1633,10 +1641,10 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.032694</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.10981</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1657,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.0008899999999999999</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
@@ -7031,7 +7039,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.136648</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>-0.010528</v>
@@ -7046,7 +7054,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002051</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>-0.0009829999999999999</v>
@@ -8403,7 +8411,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.136648</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>-0.010528</v>
@@ -8418,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002051</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>-0.0009829999999999999</v>
@@ -8461,7 +8469,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.312448</v>
+        <v>-1.449096</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.660686</v>
@@ -8476,7 +8484,7 @@
         <v>-0.126525</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.300115</v>
+        <v>-0.302166</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.150568</v>
@@ -31644,7 +31652,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -40711,7 +40723,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -42808,7 +42824,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -49531,7 +49551,11 @@
           <t>Disposition (acquisition) of equipment</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E416" s="5" t="n">
         <v>-0.136648</v>
       </c>
@@ -49931,7 +49955,11 @@
           <t>Proceeds on share issuance</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>0.9813499999999999</v>
       </c>
@@ -54412,11 +54440,7 @@
           <t>Net income (loss) from continued operations</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+      <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -54515,7 +54539,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -55596,7 +55620,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -55651,7 +55679,7 @@
         <v>-0.0008899999999999999</v>
       </c>
       <c r="P479" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0172</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -67426,7 +67454,11 @@
           <t>Net gain (loss) from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
